--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487065_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487065_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.7901</v>
+        <v>4.5409</v>
       </c>
       <c r="E2" t="n">
-        <v>3.683</v>
+        <v>2.7817</v>
       </c>
       <c r="F2" t="n">
-        <v>2.1072</v>
+        <v>1.7592</v>
       </c>
       <c r="G2" t="n">
         <v>0.6122</v>
@@ -610,13 +610,13 @@
         <v>2.1231</v>
       </c>
       <c r="S2" t="n">
-        <v>3.0042</v>
+        <v>1.7549</v>
       </c>
       <c r="T2" t="n">
-        <v>2.1192</v>
+        <v>1.2179</v>
       </c>
       <c r="U2" t="n">
-        <v>0.885</v>
+        <v>0.537</v>
       </c>
       <c r="V2" t="n">
         <v>0.2436</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.0124</v>
+        <v>3.4641</v>
       </c>
       <c r="E3" t="n">
-        <v>3.5001</v>
+        <v>3.0589</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5123</v>
+        <v>0.4052</v>
       </c>
       <c r="G3" t="n">
         <v>3.9708</v>
@@ -688,13 +688,13 @@
         <v>2.5091</v>
       </c>
       <c r="S3" t="n">
-        <v>1.7834</v>
+        <v>1.2351</v>
       </c>
       <c r="T3" t="n">
-        <v>1.5401</v>
+        <v>1.0989</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2432</v>
+        <v>0.1361</v>
       </c>
       <c r="V3" t="n">
         <v>-2.1278</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.6966</v>
+        <v>2.5826</v>
       </c>
       <c r="E4" t="n">
-        <v>2.6472</v>
+        <v>2.5064</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0494</v>
+        <v>0.0762</v>
       </c>
       <c r="G4" t="n">
         <v>0.8532999999999999</v>
@@ -766,13 +766,13 @@
         <v>2.3161</v>
       </c>
       <c r="S4" t="n">
-        <v>1.0411</v>
+        <v>0.927</v>
       </c>
       <c r="T4" t="n">
-        <v>1.3471</v>
+        <v>1.2063</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.3061</v>
+        <v>-0.2793</v>
       </c>
       <c r="V4" t="n">
         <v>-1.5138</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.2451</v>
+        <v>1.2054</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2943</v>
+        <v>0.094</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9508</v>
+        <v>1.1114</v>
       </c>
       <c r="G5" t="n">
         <v>0.8868</v>
@@ -844,13 +844,13 @@
         <v>0.772</v>
       </c>
       <c r="S5" t="n">
-        <v>0.5513</v>
+        <v>0.5116000000000001</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9333</v>
+        <v>0.7331</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3821</v>
+        <v>-0.2214</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2862</v>
+        <v>0.9336</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.0267</v>
+        <v>0.4334</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3129</v>
+        <v>0.5002</v>
       </c>
       <c r="G6" t="n">
         <v>-2.2466</v>
@@ -922,13 +922,13 @@
         <v>1.7371</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.039</v>
+        <v>0.6084000000000001</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1309</v>
+        <v>0.591</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1699</v>
+        <v>0.0175</v>
       </c>
       <c r="V6" t="n">
         <v>1.7997</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2079</v>
+        <v>0.5748</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.8884</v>
+        <v>-0.3877</v>
       </c>
       <c r="F7" t="n">
-        <v>1.0963</v>
+        <v>0.9625</v>
       </c>
       <c r="G7" t="n">
         <v>-0.1047</v>
@@ -1000,13 +1000,13 @@
         <v>0.386</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.07340000000000001</v>
+        <v>0.2935</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2829</v>
+        <v>0.2178</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2095</v>
+        <v>0.0757</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.048</v>
+        <v>-0.4075</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.0806</v>
+        <v>-2.5204</v>
       </c>
       <c r="F8" t="n">
-        <v>2.0326</v>
+        <v>2.1129</v>
       </c>
       <c r="G8" t="n">
         <v>-0.6445</v>
@@ -1078,13 +1078,13 @@
         <v>2.5091</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1104</v>
+        <v>0.5301</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1005</v>
+        <v>0.6607</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2109</v>
+        <v>-0.1306</v>
       </c>
       <c r="V8" t="n">
         <v>0.2859</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.5556</v>
+        <v>-2.2239</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.2003</v>
+        <v>-0.8418</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.3553</v>
+        <v>-1.3821</v>
       </c>
       <c r="G9" t="n">
         <v>-0.3575</v>
@@ -1156,13 +1156,13 @@
         <v>1.9301</v>
       </c>
       <c r="S9" t="n">
-        <v>1.4509</v>
+        <v>0.7826</v>
       </c>
       <c r="T9" t="n">
-        <v>1.1541</v>
+        <v>0.5125999999999999</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2967</v>
+        <v>0.27</v>
       </c>
       <c r="V9" t="n">
         <v>-2.4559</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.4784</v>
+        <v>-3.9172</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.5155</v>
+        <v>-4.115</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0371</v>
+        <v>0.1977</v>
       </c>
       <c r="G10" t="n">
         <v>-2.8221</v>
@@ -1234,13 +1234,13 @@
         <v>1.9301</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2353</v>
+        <v>0.3259</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1361</v>
+        <v>0.2644</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0992</v>
+        <v>0.0614</v>
       </c>
       <c r="V10" t="n">
         <v>-1.228</v>
@@ -1267,10 +1267,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.7634</v>
+        <v>-4.0624</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.8712</v>
+        <v>-5.1702</v>
       </c>
       <c r="F11" t="n">
         <v>1.1078</v>
@@ -1312,10 +1312,10 @@
         <v>1.158</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3265</v>
+        <v>0.3745</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4019</v>
+        <v>0.2991</v>
       </c>
       <c r="U11" t="n">
         <v>0.07530000000000001</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>2.392899999999999</v>
+        <v>2.690399999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.458099999999999</v>
+        <v>-4.160699999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>6.851100000000001</v>
+        <v>6.851</v>
       </c>
       <c r="G12" t="n">
         <v>-2.201</v>
@@ -1390,13 +1390,13 @@
         <v>17.3707</v>
       </c>
       <c r="S12" t="n">
-        <v>7.0463</v>
+        <v>7.3436</v>
       </c>
       <c r="T12" t="n">
-        <v>6.5043</v>
+        <v>6.8018</v>
       </c>
       <c r="U12" t="n">
-        <v>0.5415000000000001</v>
+        <v>0.5417000000000001</v>
       </c>
       <c r="V12" t="n">
         <v>-4.382300000000001</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.0168</v>
+        <v>5.1319</v>
       </c>
       <c r="E13" t="n">
-        <v>5.5708</v>
+        <v>6.0715</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.554</v>
+        <v>-0.9396</v>
       </c>
       <c r="G13" t="n">
         <v>2.8979</v>
@@ -1468,13 +1468,13 @@
         <v>1.3511</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.4601</v>
+        <v>-0.345</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.7297</v>
+        <v>-0.229</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.7304</v>
+        <v>-0.116</v>
       </c>
       <c r="V13" t="n">
         <v>1.228</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.9684</v>
+        <v>2.7384</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.1306</v>
+        <v>0.0697</v>
       </c>
       <c r="F14" t="n">
-        <v>3.099</v>
+        <v>2.6687</v>
       </c>
       <c r="G14" t="n">
         <v>1.1877</v>
@@ -1546,13 +1546,13 @@
         <v>2.3161</v>
       </c>
       <c r="S14" t="n">
-        <v>0.6252</v>
+        <v>0.3952</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.4045</v>
+        <v>-0.2042</v>
       </c>
       <c r="U14" t="n">
-        <v>1.0297</v>
+        <v>0.5994</v>
       </c>
       <c r="V14" t="n">
         <v>2.6996</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. DINIS</t>
+          <t>C. HERRERO SANDOVAL</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.3248</v>
+        <v>0.8538</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.9</v>
+        <v>-0.0964</v>
       </c>
       <c r="F15" t="n">
-        <v>2.2248</v>
+        <v>0.9502</v>
       </c>
       <c r="G15" t="n">
-        <v>1.5463</v>
+        <v>0.442</v>
       </c>
       <c r="H15" t="n">
-        <v>0.06619999999999999</v>
+        <v>0.442</v>
       </c>
       <c r="I15" t="n">
-        <v>1.4801</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>0.6917</v>
+        <v>0.0414</v>
       </c>
       <c r="K15" t="n">
-        <v>0.6674</v>
+        <v>0.0414</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0243</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>0.8547</v>
+        <v>0.4006</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.6012</v>
+        <v>0.4006</v>
       </c>
       <c r="O15" t="n">
-        <v>1.4559</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.158</v>
+        <v>0.772</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.8951</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.7371</v>
+        <v>0.772</v>
       </c>
       <c r="S15" t="n">
-        <v>0.8943</v>
+        <v>-0.3602</v>
       </c>
       <c r="T15" t="n">
-        <v>1.3035</v>
+        <v>-0.1378</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.4092</v>
+        <v>-0.2224</v>
       </c>
       <c r="V15" t="n">
-        <v>0.0422</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0.0422</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>C. HERRERO SANDOVAL</t>
+          <t>J. DOSS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.7268</v>
+        <v>0.6891</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.1966</v>
+        <v>-1.5297</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9234</v>
+        <v>2.2189</v>
       </c>
       <c r="G16" t="n">
-        <v>0.442</v>
+        <v>1.6486</v>
       </c>
       <c r="H16" t="n">
-        <v>0.442</v>
+        <v>0.9923999999999999</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>0.6562</v>
       </c>
       <c r="J16" t="n">
-        <v>0.0414</v>
+        <v>1.3012</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0414</v>
+        <v>1.961</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>-0.6597</v>
       </c>
       <c r="M16" t="n">
-        <v>0.4006</v>
+        <v>0.3474</v>
       </c>
       <c r="N16" t="n">
-        <v>0.4006</v>
+        <v>-0.9685</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>1.3159</v>
       </c>
       <c r="P16" t="n">
-        <v>0.772</v>
+        <v>-0.386</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-2.8951</v>
       </c>
       <c r="R16" t="n">
-        <v>0.772</v>
+        <v>2.5091</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.4871</v>
+        <v>-0.9016</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.238</v>
+        <v>-0.2217</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2492</v>
+        <v>-0.6798999999999999</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>0.3281</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>0.2859</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>0.0422</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. DOSS</t>
+          <t>A. DINIS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.2528</v>
+        <v>0.5832000000000001</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.4296</v>
+        <v>-1.8012</v>
       </c>
       <c r="F17" t="n">
-        <v>1.1768</v>
+        <v>2.3844</v>
       </c>
       <c r="G17" t="n">
-        <v>1.6486</v>
+        <v>1.5463</v>
       </c>
       <c r="H17" t="n">
-        <v>0.9923999999999999</v>
+        <v>0.06619999999999999</v>
       </c>
       <c r="I17" t="n">
-        <v>0.6562</v>
+        <v>1.4801</v>
       </c>
       <c r="J17" t="n">
-        <v>1.3012</v>
+        <v>0.6917</v>
       </c>
       <c r="K17" t="n">
-        <v>1.961</v>
+        <v>0.6674</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.6597</v>
+        <v>0.0243</v>
       </c>
       <c r="M17" t="n">
-        <v>0.3474</v>
+        <v>0.8547</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.9685</v>
+        <v>-0.6012</v>
       </c>
       <c r="O17" t="n">
-        <v>1.3159</v>
+        <v>1.4559</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.386</v>
+        <v>-1.158</v>
       </c>
       <c r="Q17" t="n">
         <v>-2.8951</v>
       </c>
       <c r="R17" t="n">
-        <v>2.5091</v>
+        <v>1.7371</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.8435</v>
+        <v>0.1527</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1216</v>
+        <v>0.4022</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.7219</v>
+        <v>-0.2496</v>
       </c>
       <c r="V17" t="n">
-        <v>0.3281</v>
+        <v>0.0422</v>
       </c>
       <c r="W17" t="n">
-        <v>0.2859</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
         <v>0.0422</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. MARCOS SÁNCHEZ</t>
+          <t>J. MORAN HUETE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.3632</v>
+        <v>0.0852</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.238</v>
+        <v>-0.4984</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.1252</v>
+        <v>0.5836</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.3539</v>
+        <v>-2.631</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.4875</v>
+        <v>-0.0391</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1335</v>
+        <v>-2.5919</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>-1.5569</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>0.8694</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>-2.4262</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.3539</v>
+        <v>-1.0742</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.4875</v>
+        <v>-0.9085</v>
       </c>
       <c r="O18" t="n">
-        <v>0.1335</v>
+        <v>-0.1657</v>
       </c>
       <c r="P18" t="n">
-        <v>0.193</v>
+        <v>2.8951</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.193</v>
+        <v>2.8951</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2023</v>
+        <v>-1.121</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.238</v>
+        <v>-0.4554</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0357</v>
+        <v>-0.6656</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.9421</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.5138</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.5717</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. MORAN HUETE</t>
+          <t>A. MARCOS SÁNCHEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.5316</v>
+        <v>-0.3096</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.0992</v>
+        <v>-0.238</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.4324</v>
+        <v>-0.0717</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.631</v>
+        <v>-0.3539</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.0391</v>
+        <v>-0.4875</v>
       </c>
       <c r="I19" t="n">
-        <v>-2.5919</v>
+        <v>0.1335</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.5569</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0.8694</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>-2.4262</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.0742</v>
+        <v>-0.3539</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.9085</v>
+        <v>-0.4875</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.1657</v>
+        <v>0.1335</v>
       </c>
       <c r="P19" t="n">
-        <v>2.8951</v>
+        <v>0.193</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.8951</v>
+        <v>0.193</v>
       </c>
       <c r="S19" t="n">
-        <v>-2.7378</v>
+        <v>-0.1487</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.0562</v>
+        <v>-0.238</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.6816</v>
+        <v>0.0892</v>
       </c>
       <c r="V19" t="n">
-        <v>0.9421</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.5138</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.5717</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>K. DOMINGOS</t>
+          <t>D. BARROSO VALVERDE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.7689</v>
+        <v>-1.9846</v>
       </c>
       <c r="E20" t="n">
-        <v>0.91</v>
+        <v>-4.3733</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.6789</v>
+        <v>2.3888</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.6076</v>
+        <v>0.1567</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.6518</v>
+        <v>0.2495</v>
       </c>
       <c r="I20" t="n">
-        <v>0.0443</v>
+        <v>-0.09279999999999999</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.0658</v>
+        <v>-1.4653</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.2693</v>
+        <v>0.4968</v>
       </c>
       <c r="L20" t="n">
-        <v>0.2035</v>
+        <v>-1.9621</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.5418</v>
+        <v>1.622</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.3825</v>
+        <v>-0.2473</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.1592</v>
+        <v>1.8693</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.579</v>
+        <v>-1.158</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.9301</v>
+        <v>-2.8951</v>
       </c>
       <c r="R20" t="n">
-        <v>1.3511</v>
+        <v>1.7371</v>
       </c>
       <c r="S20" t="n">
-        <v>0.4178</v>
+        <v>-0.4115</v>
       </c>
       <c r="T20" t="n">
-        <v>1.3921</v>
+        <v>-0.0129</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.9743000000000001</v>
+        <v>-0.3986</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-0.5717</v>
       </c>
       <c r="W20" t="n">
-        <v>1.5138</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.5138</v>
+        <v>-0.5717</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>D. BARROSO VALVERDE</t>
+          <t>K. DOMINGOS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.0979</v>
+        <v>-2.3092</v>
       </c>
       <c r="E21" t="n">
-        <v>-4.2732</v>
+        <v>-0.1915</v>
       </c>
       <c r="F21" t="n">
-        <v>2.1753</v>
+        <v>-2.1177</v>
       </c>
       <c r="G21" t="n">
-        <v>0.1567</v>
+        <v>-1.6076</v>
       </c>
       <c r="H21" t="n">
-        <v>0.2495</v>
+        <v>-1.6518</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.09279999999999999</v>
+        <v>0.0443</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.4653</v>
+        <v>-0.0658</v>
       </c>
       <c r="K21" t="n">
-        <v>0.4968</v>
+        <v>-0.2693</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.9621</v>
+        <v>0.2035</v>
       </c>
       <c r="M21" t="n">
-        <v>1.622</v>
+        <v>-1.5418</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.2473</v>
+        <v>-1.3825</v>
       </c>
       <c r="O21" t="n">
-        <v>1.8693</v>
+        <v>-0.1592</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.158</v>
+        <v>-0.579</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.8951</v>
+        <v>-1.9301</v>
       </c>
       <c r="R21" t="n">
-        <v>1.7371</v>
+        <v>1.3511</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.5248</v>
+        <v>-0.1226</v>
       </c>
       <c r="T21" t="n">
-        <v>0.0873</v>
+        <v>0.2905</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.6121</v>
+        <v>-0.4131</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.5717</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.5138</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.5717</v>
+        <v>-1.5138</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.4155</v>
+        <v>-3.8655</v>
       </c>
       <c r="E22" t="n">
-        <v>-5.0649</v>
+        <v>-4.2638</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.3506</v>
+        <v>0.3983</v>
       </c>
       <c r="G22" t="n">
         <v>-1.0857</v>
@@ -2170,13 +2170,13 @@
         <v>0.579</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.7278</v>
+        <v>-0.1778</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5367</v>
+        <v>0.2644</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.1911</v>
+        <v>-0.4422</v>
       </c>
       <c r="V22" t="n">
         <v>-0.2859</v>
@@ -2203,16 +2203,16 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.3931</v>
+        <v>1.612699999999999</v>
       </c>
       <c r="E23" t="n">
-        <v>-6.851299999999999</v>
+        <v>-6.851099999999999</v>
       </c>
       <c r="F23" t="n">
-        <v>4.4582</v>
+        <v>8.463900000000001</v>
       </c>
       <c r="G23" t="n">
-        <v>2.200999999999999</v>
+        <v>2.201</v>
       </c>
       <c r="H23" t="n">
         <v>-5.1748</v>
@@ -2233,10 +2233,10 @@
         <v>-1.3333</v>
       </c>
       <c r="N23" t="n">
-        <v>-9.1839</v>
+        <v>-9.183900000000001</v>
       </c>
       <c r="O23" t="n">
-        <v>7.8505</v>
+        <v>7.850499999999999</v>
       </c>
       <c r="P23" t="n">
         <v>-1.93</v>
@@ -2248,13 +2248,13 @@
         <v>15.4407</v>
       </c>
       <c r="S23" t="n">
-        <v>-7.0461</v>
+        <v>-3.0405</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.5418000000000001</v>
+        <v>-0.5419</v>
       </c>
       <c r="U23" t="n">
-        <v>-6.5044</v>
+        <v>-2.4988</v>
       </c>
       <c r="V23" t="n">
         <v>4.382400000000001</v>
